--- a/Battery Charger Project/Excel/BOM/BOM V2.xlsx
+++ b/Battery Charger Project/Excel/BOM/BOM V2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Verrazano\Acedemic\Research\Battery-Charger\Battery Charger Project\Excel\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A47C73A6-13BF-4DCA-9E11-029305F8741F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6CCFE87-39C7-4B68-B19D-259979B8E9F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>item use</t>
   </si>
@@ -81,16 +81,42 @@
   </si>
   <si>
     <t>Three phase rectifier</t>
+  </si>
+  <si>
+    <t>link</t>
+  </si>
+  <si>
+    <t>Bridge Rectifiers Bridge, 3phase, DB, 200V, 15A, 150C, 350A</t>
+  </si>
+  <si>
+    <t>DB15-02</t>
+  </si>
+  <si>
+    <t>860020672009</t>
+  </si>
+  <si>
+    <t>Diotec Semiconductor</t>
+  </si>
+  <si>
+    <t>https://www.mouser.com/en/ProductDetail/Diotec-Semiconductor/DB15-02?qs=OlC7AqGiEDmue9J3fser1A%3D%3D</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -113,16 +139,25 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -136,16 +171,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BE2F4241-DD34-429E-8619-5EC72E0D5702}" name="Table1" displayName="Table1" ref="B1:G3" totalsRowShown="0">
-  <autoFilter ref="B1:G3" xr:uid="{BE2F4241-DD34-429E-8619-5EC72E0D5702}"/>
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BE2F4241-DD34-429E-8619-5EC72E0D5702}" name="Table1" displayName="Table1" ref="A1:H4" totalsRowShown="0">
+  <autoFilter ref="A1:H4" xr:uid="{BE2F4241-DD34-429E-8619-5EC72E0D5702}"/>
+  <tableColumns count="8">
+    <tableColumn id="7" xr3:uid="{753B9BB0-B725-40B1-B016-495A15E17260}" name="item use"/>
     <tableColumn id="1" xr3:uid="{C3813DDA-4FC9-4A06-81E6-4B3D0E0DB3F4}" name="Item description"/>
     <tableColumn id="2" xr3:uid="{0F29471E-8450-4076-A11B-42E60513268E}" name="product number"/>
     <tableColumn id="3" xr3:uid="{5235EA40-33F9-4337-B7AF-72A732137026}" name="vendor"/>
+    <tableColumn id="8" xr3:uid="{E9AD782F-B631-439F-8AEA-B1DBE224FC4B}" name="link"/>
     <tableColumn id="4" xr3:uid="{F817B8B8-F62B-4AED-A59D-A4A7A27FEF20}" name="quantity"/>
     <tableColumn id="5" xr3:uid="{667F21B1-6936-4832-9511-B62ACA607FAB}" name="unit price"/>
-    <tableColumn id="6" xr3:uid="{F093F0CF-BEF4-46EF-A09E-6030BDB5EDEC}" name="Total cost">
-      <calculatedColumnFormula>E2*F2</calculatedColumnFormula>
+    <tableColumn id="6" xr3:uid="{F093F0CF-BEF4-46EF-A09E-6030BDB5EDEC}" name="Total cost" dataDxfId="0">
+      <calculatedColumnFormula>F2*G2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -415,19 +452,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5546875" customWidth="1"/>
+    <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="98.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.44140625" customWidth="1"/>
     <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -441,16 +479,19 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -463,50 +504,75 @@
       <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>3</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>24.05</v>
       </c>
-      <c r="G2">
-        <f>E2*F2</f>
+      <c r="H2">
+        <f t="shared" ref="H2:H4" si="0">F2*G2</f>
         <v>72.150000000000006</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
       </c>
-      <c r="C3">
-        <v>860020672009</v>
+      <c r="C3" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>10</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>0.11</v>
       </c>
-      <c r="G3">
-        <f>E3*F3</f>
+      <c r="H3">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3">
+        <v>9.2799999999999994</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="0"/>
+        <v>9.2799999999999994</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E4" r:id="rId1" xr:uid="{834A813A-2921-4DBA-951C-4D613A5B8572}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Battery Charger Project/Excel/BOM/BOM V2.xlsx
+++ b/Battery Charger Project/Excel/BOM/BOM V2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Verrazano\Acedemic\Research\Battery-Charger\Battery Charger Project\Excel\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A47C73A6-13BF-4DCA-9E11-029305F8741F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE622F0-70CD-4C8A-B61E-3444A5500DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>item use</t>
   </si>
@@ -74,26 +74,61 @@
     <t>Buck capacitor</t>
   </si>
   <si>
-    <t>CAP ALUM 6.8UF 20% 50V RADIAL TH</t>
-  </si>
-  <si>
     <t>Würth Elektronik</t>
   </si>
   <si>
     <t>Three phase rectifier</t>
+  </si>
+  <si>
+    <t>link</t>
+  </si>
+  <si>
+    <t>Bridge Rectifiers Bridge, 3phase, DB, 200V, 15A, 150C, 350A</t>
+  </si>
+  <si>
+    <t>DB15-02</t>
+  </si>
+  <si>
+    <t>Diotec Semiconductor</t>
+  </si>
+  <si>
+    <t>https://www.mouser.com/en/ProductDetail/Diotec-Semiconductor/DB15-02?qs=OlC7AqGiEDmue9J3fser1A%3D%3D</t>
+  </si>
+  <si>
+    <t>CAP ALUM 10UF 20% 35V RADIAL TH</t>
+  </si>
+  <si>
+    <t>860020572003</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/w%C3%BCrth-elektronik/860020572003/5727172</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -113,16 +148,27 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -136,16 +182,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BE2F4241-DD34-429E-8619-5EC72E0D5702}" name="Table1" displayName="Table1" ref="B1:G3" totalsRowShown="0">
-  <autoFilter ref="B1:G3" xr:uid="{BE2F4241-DD34-429E-8619-5EC72E0D5702}"/>
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BE2F4241-DD34-429E-8619-5EC72E0D5702}" name="Table1" displayName="Table1" ref="A1:H4" totalsRowShown="0">
+  <autoFilter ref="A1:H4" xr:uid="{BE2F4241-DD34-429E-8619-5EC72E0D5702}"/>
+  <tableColumns count="8">
+    <tableColumn id="7" xr3:uid="{753B9BB0-B725-40B1-B016-495A15E17260}" name="item use"/>
     <tableColumn id="1" xr3:uid="{C3813DDA-4FC9-4A06-81E6-4B3D0E0DB3F4}" name="Item description"/>
     <tableColumn id="2" xr3:uid="{0F29471E-8450-4076-A11B-42E60513268E}" name="product number"/>
     <tableColumn id="3" xr3:uid="{5235EA40-33F9-4337-B7AF-72A732137026}" name="vendor"/>
+    <tableColumn id="8" xr3:uid="{E9AD782F-B631-439F-8AEA-B1DBE224FC4B}" name="link"/>
     <tableColumn id="4" xr3:uid="{F817B8B8-F62B-4AED-A59D-A4A7A27FEF20}" name="quantity"/>
     <tableColumn id="5" xr3:uid="{667F21B1-6936-4832-9511-B62ACA607FAB}" name="unit price"/>
-    <tableColumn id="6" xr3:uid="{F093F0CF-BEF4-46EF-A09E-6030BDB5EDEC}" name="Total cost">
-      <calculatedColumnFormula>E2*F2</calculatedColumnFormula>
+    <tableColumn id="6" xr3:uid="{F093F0CF-BEF4-46EF-A09E-6030BDB5EDEC}" name="Total cost" dataDxfId="0">
+      <calculatedColumnFormula>F2*G2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -415,19 +463,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5546875" customWidth="1"/>
+    <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="98.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.44140625" customWidth="1"/>
     <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -441,16 +490,19 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -463,50 +515,79 @@
       <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>3</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>24.05</v>
       </c>
-      <c r="G2">
-        <f>E2*F2</f>
+      <c r="H2">
+        <f t="shared" ref="H2:H3" si="0">F2*G2</f>
         <v>72.150000000000006</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3">
+        <v>9.2799999999999994</v>
+      </c>
+      <c r="H3">
+        <f t="shared" si="0"/>
+        <v>9.2799999999999994</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
         <v>12</v>
       </c>
-      <c r="C3">
-        <v>860020672009</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3">
+      <c r="E4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4">
         <v>10</v>
       </c>
-      <c r="F3">
-        <v>0.11</v>
-      </c>
-      <c r="G3">
-        <f>E3*F3</f>
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>14</v>
+      <c r="G4" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="H4" s="4">
+        <f>F4*G4</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E3" r:id="rId1" xr:uid="{834A813A-2921-4DBA-951C-4D613A5B8572}"/>
+    <hyperlink ref="E4" r:id="rId2" xr:uid="{731E9BA3-84A5-4BF3-B19A-5D7D51647ABD}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Battery Charger Project/Excel/BOM/BOM V2.xlsx
+++ b/Battery Charger Project/Excel/BOM/BOM V2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Verrazano\Acedemic\Research\Battery-Charger\Battery Charger Project\Excel\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE622F0-70CD-4C8A-B61E-3444A5500DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB2FCED1-B5E2-45D0-9461-7703E59CDD71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -152,12 +152,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -572,10 +571,10 @@
       <c r="F4">
         <v>10</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="4">
         <v>0.1</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4">
         <f>F4*G4</f>
         <v>1</v>
       </c>
